--- a/notion-import-templates/Coverage_Update_Template.xlsx
+++ b/notion-import-templates/Coverage_Update_Template.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BE6EE74-092C-4309-B9FF-6FE7B422230A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Coverage Update" state="visible" r:id="rId4"/>
+    <sheet name="Coverage Update" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="52">
   <si>
     <t>Bill Morrisons — Coverage Amounts Update</t>
   </si>
@@ -52,7 +56,10 @@
     <t>🏥 Medical Class</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-814f-925b-f83bf6243606</t>
+    <t>366de6dd-1dfe-8099-b550-dc560f95a221</t>
+  </si>
+  <si>
+    <t>366de6dd-1dfe-81e7-80ab-ea6995cdbb4e</t>
   </si>
   <si>
     <t>DAMIEN NG TZE HOONG</t>
@@ -67,13 +74,13 @@
     <t>🛡️ Life Cover, ❤️ Critical Illness (CI), ♿ TPD</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-81d5-8918-caf9a9396ec1</t>
+    <t>366de6dd-1dfe-8174-a6a8-dae69d8b06dc</t>
   </si>
   <si>
     <t>🛡️ Life Cover, ⏸️ Waiver of Premium, ❤️ Critical Illness (CI), ♿ TPD, 🏥 Medical</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-81d7-a139-cde24e259d4c</t>
+    <t>366de6dd-1dfe-8104-ae2a-dc264f3fc79e</t>
   </si>
   <si>
     <t>Smart Link - Basic</t>
@@ -85,7 +92,7 @@
     <t>🛡️ Life Cover, ♿ TPD</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-81d0-8acb-c9833b7a9c38</t>
+    <t>366de6dd-1dfe-8188-888b-fcddcc8a94e0</t>
   </si>
   <si>
     <t>KAM BENG SIM</t>
@@ -94,7 +101,7 @@
     <t>🛡️ Life Cover, ⏸️ Waiver of Premium, ♿ TPD, 🏥 Medical</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-81b9-91e6-c474d325a8e2</t>
+    <t>366de6dd-1dfe-8167-acb9-fb840ec04f25</t>
   </si>
   <si>
     <t>KAREN CHEW AI LENG</t>
@@ -103,13 +110,13 @@
     <t>AssuredLink</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-8145-98be-db573a8b8c90</t>
+    <t>366de6dd-1dfe-8183-bbb7-f99173a8cb2f</t>
   </si>
   <si>
     <t>🛡️ Life Cover, ⏸️ Waiver of Premium, ❤️ Critical Illness (CI), ♿ TPD</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-8115-a8f5-ec1cba603641</t>
+    <t>366de6dd-1dfe-8194-a719-d14edb7829c8</t>
   </si>
   <si>
     <t>LEONG CHEE KEONG</t>
@@ -118,19 +125,19 @@
     <t>🛡️ Life Cover, ♿ TPD, 🏥 Medical</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-81d4-948a-eb578a5eddfd</t>
-  </si>
-  <si>
-    <t>366de6dd-1dfe-8189-9c35-eea57261d1e1</t>
+    <t>366de6dd-1dfe-81d0-a935-e50bcabfdec2</t>
+  </si>
+  <si>
+    <t>366de6dd-1dfe-81ab-b570-cbef0dfda05b</t>
   </si>
   <si>
     <t>🛡️ Life Cover, ⏸️ Waiver of Premium, ♿ TPD</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-813e-87e9-d706cbbe2ed5</t>
-  </si>
-  <si>
-    <t>366de6dd-1dfe-81aa-9fc2-c96b48184ab8</t>
+    <t>366de6dd-1dfe-81e4-a46e-eae5fa52d689</t>
+  </si>
+  <si>
+    <t>366de6dd-1dfe-81ad-b04e-dc25aeef8e9e</t>
   </si>
   <si>
     <t>PRUAll Care</t>
@@ -142,7 +149,7 @@
     <t>🛡️ Life Cover, ⏸️ Waiver of Premium</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-81ab-a762-dc02280612ae</t>
+    <t>366de6dd-1dfe-814e-ba62-c44acae954d0</t>
   </si>
   <si>
     <t>PRUWealth</t>
@@ -151,16 +158,16 @@
     <t>🛡️ Life Cover, 🦺 Personal Accident</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-814e-ba46-d8ed549a854a</t>
+    <t>366de6dd-1dfe-814e-b481-f77f087375d9</t>
   </si>
   <si>
     <t>NG MEI CHING</t>
   </si>
   <si>
-    <t>366de6dd-1dfe-817b-8adc-fe7d3285ba1e</t>
-  </si>
-  <si>
-    <t>366de6dd-1dfe-81b0-9ca2-c9d0f268f45c</t>
+    <t>366de6dd-1dfe-8170-99c2-e0c8578d5459</t>
+  </si>
+  <si>
+    <t>366de6dd-1dfe-81fa-9c9c-e61e79dbeedb</t>
   </si>
   <si>
     <t>* Page ID is used by the import script to update the correct Notion record. Do not modify.</t>
@@ -169,45 +176,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1A1A2E"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF1A1A2E"/>
-      <sz val="14"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF666666"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="FFCCCCCC"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <b/>
-    </font>
-    <font>
-      <color rgb="FF6B7280"/>
-    </font>
-    <font/>
-    <font>
-      <i/>
       <color rgb="FF9CA3AF"/>
-      <sz val="9"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -288,14 +307,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -308,13 +321,25 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -653,462 +678,627 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="5" max="5" width="70.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+    </row>
+    <row r="3" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="7">
+      <c r="E5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="4">
         <v>150000</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="G5" s="10">
+        <v>150000</v>
+      </c>
+      <c r="H5" s="10">
+        <v>150000</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>150000</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4">
+        <v>100000</v>
+      </c>
+      <c r="G6" s="10">
+        <v>100000</v>
+      </c>
+      <c r="H6" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="10">
+        <v>100000</v>
+      </c>
+      <c r="K6" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="4">
+        <v>10000</v>
+      </c>
+      <c r="G8" s="10">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="10">
+        <v>10000</v>
+      </c>
+      <c r="K8" s="5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="4">
+        <v>5000</v>
+      </c>
+      <c r="G9" s="10">
+        <v>5000</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="10">
+        <v>5000</v>
+      </c>
+      <c r="K9" s="5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="4">
+        <v>50000</v>
+      </c>
+      <c r="G10" s="10">
+        <v>50000</v>
+      </c>
+      <c r="H10" s="10">
+        <v>150000</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="10">
+        <v>50000</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="4">
+        <v>5000</v>
+      </c>
+      <c r="G11" s="10">
+        <v>5000</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="10">
+        <v>5000</v>
+      </c>
+      <c r="K11" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="4">
+        <v>5000</v>
+      </c>
+      <c r="G12" s="10">
+        <v>5000</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="10">
+        <v>5000</v>
+      </c>
+      <c r="K12" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="4">
+        <v>200000</v>
+      </c>
+      <c r="G13" s="10">
+        <v>200000</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="10">
+        <v>200000</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="F14" s="4">
+        <v>100000</v>
+      </c>
+      <c r="G14" s="10">
+        <v>100000</v>
+      </c>
+      <c r="H14" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="10">
+        <v>100000</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="4">
+        <v>100000</v>
+      </c>
+      <c r="G15" s="11">
+        <v>100000</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="G16" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11">
+        <v>1000000</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="4">
+        <v>5000</v>
+      </c>
+      <c r="G17" s="10">
+        <v>5000</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="10">
+        <v>5000</v>
+      </c>
+      <c r="K17" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="D18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="4">
         <v>100000</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="G18" s="10">
+        <v>100000</v>
+      </c>
+      <c r="H18" s="10">
+        <v>150000</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="10">
+        <v>100000</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="4">
         <v>1000000</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="7">
-        <v>10000</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="7">
-        <v>5000</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="7">
-        <v>50000</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="7">
-        <v>5000</v>
-      </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="7">
-        <v>5000</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="7">
-        <v>200000</v>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="7">
-        <v>100000</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="7">
-        <v>100000</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="G19" s="11">
         <v>1000000</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="7">
-        <v>5000</v>
-      </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="7">
-        <v>100000</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="11">
         <v>1000000</v>
       </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>50</v>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1117,6 +1307,6 @@
     <mergeCell ref="A2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>